--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmddu\Documents\pension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20787309-7DD5-4654-AE5C-DCE2043D8FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594C7A3E-6E17-4B5C-8290-3F068D9D0C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,6 +493,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="23.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.6">
       <c r="B1" s="1" t="s">
@@ -567,16 +570,16 @@
         <v>0.1238770856905482</v>
       </c>
       <c r="C5">
-        <v>2.122977487451179E-4</v>
+        <v>1.2430551098370921E-2</v>
       </c>
       <c r="D5">
-        <v>0.93499931264517999</v>
+        <v>0.56145359913431514</v>
       </c>
       <c r="E5">
         <v>0.50649881967229782</v>
       </c>
       <c r="F5">
-        <v>0.1094465972119656</v>
+        <v>0.18226349127038191</v>
       </c>
       <c r="G5">
         <v>3.7565087755339933E-2</v>
@@ -593,16 +596,16 @@
         <v>0.1136322568729118</v>
       </c>
       <c r="C6">
-        <v>1.732719905971953E-4</v>
+        <v>1.247877548620561E-2</v>
       </c>
       <c r="D6">
-        <v>0.93899681287636927</v>
+        <v>0.56549630209150337</v>
       </c>
       <c r="E6">
         <v>0.46025184176921391</v>
       </c>
       <c r="F6">
-        <v>9.8070262948836862E-2</v>
+        <v>0.16284397264193701</v>
       </c>
       <c r="G6">
         <v>3.3738566246329281E-2</v>
@@ -619,16 +622,16 @@
         <v>0.15828401171305129</v>
       </c>
       <c r="C7">
-        <v>3.2743116936386179E-4</v>
+        <v>1.298051670437201E-2</v>
       </c>
       <c r="D7">
-        <v>0.96657204595453028</v>
+        <v>0.58145623667555646</v>
       </c>
       <c r="E7">
         <v>0.66146998598808793</v>
       </c>
       <c r="F7">
-        <v>0.1414684189961328</v>
+        <v>0.2351671726299554</v>
       </c>
       <c r="G7">
         <v>5.4230988994801117E-2</v>
@@ -645,16 +648,16 @@
         <v>0.14778204500748671</v>
       </c>
       <c r="C8">
-        <v>2.9389695778787579E-4</v>
+        <v>1.26696437322277E-2</v>
       </c>
       <c r="D8">
-        <v>0.94822152951516581</v>
+        <v>0.56867616464417603</v>
       </c>
       <c r="E8">
         <v>0.61886440015857658</v>
       </c>
       <c r="F8">
-        <v>0.13313075958739989</v>
+        <v>0.22198477856104221</v>
       </c>
       <c r="G8">
         <v>4.9048021082865829E-2</v>
@@ -671,16 +674,16 @@
         <v>0.1235219020533762</v>
       </c>
       <c r="C9">
-        <v>2.1074923116039959E-4</v>
+        <v>1.237635424817078E-2</v>
       </c>
       <c r="D9">
-        <v>0.93085079553695882</v>
+        <v>0.55903579140740145</v>
       </c>
       <c r="E9">
         <v>0.50902327282057658</v>
       </c>
       <c r="F9">
-        <v>0.1095527983821987</v>
+        <v>0.18241642323228821</v>
       </c>
       <c r="G9">
         <v>3.7792244383301317E-2</v>
@@ -697,16 +700,16 @@
         <v>0.14906104688746361</v>
       </c>
       <c r="C10">
-        <v>2.9559129468054819E-4</v>
+        <v>1.2845770889391209E-2</v>
       </c>
       <c r="D10">
-        <v>0.96062277771813709</v>
+        <v>0.57670350856949515</v>
       </c>
       <c r="E10">
         <v>0.62292584601240863</v>
       </c>
       <c r="F10">
-        <v>0.13274352567858069</v>
+        <v>0.22111267309220961</v>
       </c>
       <c r="G10">
         <v>5.0580261194540253E-2</v>
@@ -723,16 +726,16 @@
         <v>0.1468708778877921</v>
       </c>
       <c r="C11">
-        <v>2.9024012348826669E-4</v>
+        <v>1.262504851388172E-2</v>
       </c>
       <c r="D11">
-        <v>0.94405544047477907</v>
+        <v>0.56680783628340892</v>
       </c>
       <c r="E11">
         <v>0.62033234380877944</v>
       </c>
       <c r="F11">
-        <v>0.1327530990115974</v>
+        <v>0.221108949698997</v>
       </c>
       <c r="G11">
         <v>4.9364241528542872E-2</v>
@@ -749,16 +752,16 @@
         <v>0.1238770856905482</v>
       </c>
       <c r="C12">
-        <v>3.2751527509470782E-4</v>
+        <v>1.289900804266606E-2</v>
       </c>
       <c r="D12">
-        <v>0.80199116944810578</v>
+        <v>0.5807134834396771</v>
       </c>
       <c r="E12">
         <v>0.50649881967229782</v>
       </c>
       <c r="F12">
-        <v>0.12759802983237631</v>
+        <v>0.17621855886384241</v>
       </c>
       <c r="G12">
         <v>6.9146575818306244E-2</v>
@@ -775,16 +778,16 @@
         <v>0.1136322568729118</v>
       </c>
       <c r="C13">
-        <v>2.9063709068238868E-4</v>
+        <v>1.2787371219841699E-2</v>
       </c>
       <c r="D13">
-        <v>0.79545065621735656</v>
+        <v>0.57727389493158465</v>
       </c>
       <c r="E13">
         <v>0.46025184176921391</v>
       </c>
       <c r="F13">
-        <v>0.1157679154918472</v>
+        <v>0.15952161557178851</v>
       </c>
       <c r="G13">
         <v>6.2500308289857545E-2</v>
@@ -801,16 +804,16 @@
         <v>0.15828401171305129</v>
       </c>
       <c r="C14">
-        <v>4.492408544603877E-4</v>
+        <v>1.32114608101661E-2</v>
       </c>
       <c r="D14">
-        <v>0.81279882486875465</v>
+        <v>0.58953425995823749</v>
       </c>
       <c r="E14">
         <v>0.66146998598808793</v>
       </c>
       <c r="F14">
-        <v>0.1682327963615407</v>
+        <v>0.2319448223360783</v>
       </c>
       <c r="G14">
         <v>8.7586543952278967E-2</v>
@@ -827,16 +830,16 @@
         <v>0.14778204500748671</v>
       </c>
       <c r="C15">
-        <v>4.1212281255622999E-4</v>
+        <v>1.302372827069514E-2</v>
       </c>
       <c r="D15">
-        <v>0.80502560090513775</v>
+        <v>0.58256271919123459</v>
       </c>
       <c r="E15">
         <v>0.61886440015857658</v>
       </c>
       <c r="F15">
-        <v>0.1568117241731741</v>
+        <v>0.2166933247234466</v>
       </c>
       <c r="G15">
         <v>8.223412903173663E-2</v>
@@ -853,16 +856,16 @@
         <v>0.1235219020533762</v>
       </c>
       <c r="C16">
-        <v>3.2622663407155941E-4</v>
+        <v>1.2771919301926201E-2</v>
       </c>
       <c r="D16">
-        <v>0.79378786216385455</v>
+        <v>0.57490379353624887</v>
       </c>
       <c r="E16">
         <v>0.50902327282057658</v>
       </c>
       <c r="F16">
-        <v>0.12846922255699531</v>
+        <v>0.17738152135004101</v>
       </c>
       <c r="G16">
         <v>6.7688853612748734E-2</v>
@@ -879,16 +882,16 @@
         <v>0.14906104688746361</v>
       </c>
       <c r="C17">
-        <v>4.1746310459602842E-4</v>
+        <v>1.3009057991038049E-2</v>
       </c>
       <c r="D17">
-        <v>0.80290545457929396</v>
+        <v>0.58164491129978857</v>
       </c>
       <c r="E17">
         <v>0.62292584601240863</v>
       </c>
       <c r="F17">
-        <v>0.15881876705928361</v>
+        <v>0.21923419578536149</v>
       </c>
       <c r="G17">
         <v>8.0508715895516808E-2</v>
@@ -905,16 +908,16 @@
         <v>0.1468708778877921</v>
       </c>
       <c r="C18">
-        <v>4.088144385580168E-4</v>
+        <v>1.2894230087386421E-2</v>
       </c>
       <c r="D18">
-        <v>0.79626056002027323</v>
+        <v>0.5767391884404327</v>
       </c>
       <c r="E18">
         <v>0.62033234380877944</v>
       </c>
       <c r="F18">
-        <v>0.1573935614224001</v>
+        <v>0.2173014906455063</v>
       </c>
       <c r="G18">
         <v>8.0526721691101616E-2</v>
@@ -931,16 +934,16 @@
         <v>0.1238770856905482</v>
       </c>
       <c r="C19">
-        <v>1.966273895103378E-4</v>
+        <v>1.161049466344297E-2</v>
       </c>
       <c r="D19">
-        <v>0.84060079565113555</v>
+        <v>0.52418022035980449</v>
       </c>
       <c r="E19">
         <v>0.50649881967229782</v>
       </c>
       <c r="F19">
-        <v>0.12173732608148941</v>
+        <v>0.19522387375528841</v>
       </c>
       <c r="G19">
         <v>2.754643408493343E-2</v>
@@ -957,16 +960,16 @@
         <v>0.1136322568729118</v>
       </c>
       <c r="C20">
-        <v>1.56992730957709E-4</v>
+        <v>1.167528913214327E-2</v>
       </c>
       <c r="D20">
-        <v>0.84592002299249547</v>
+        <v>0.52901113368781638</v>
       </c>
       <c r="E20">
         <v>0.46025184176921391</v>
       </c>
       <c r="F20">
-        <v>0.10886095829856279</v>
+        <v>0.17407509687924391</v>
       </c>
       <c r="G20">
         <v>2.3805202969911839E-2</v>
@@ -983,16 +986,16 @@
         <v>0.15828401171305129</v>
       </c>
       <c r="C21">
-        <v>3.1090190330678168E-4</v>
+        <v>1.2144932179444821E-2</v>
       </c>
       <c r="D21">
-        <v>0.87003579266042619</v>
+        <v>0.54349842633377354</v>
       </c>
       <c r="E21">
         <v>0.66146998598808793</v>
       </c>
       <c r="F21">
-        <v>0.15716528025693999</v>
+        <v>0.25159119615016201</v>
       </c>
       <c r="G21">
         <v>4.2364673564864723E-2</v>
@@ -1009,16 +1012,16 @@
         <v>0.14778204500748671</v>
       </c>
       <c r="C22">
-        <v>2.7740979287525731E-4</v>
+        <v>1.186307384924783E-2</v>
       </c>
       <c r="D22">
-        <v>0.85438310385224558</v>
+        <v>0.53205327832827398</v>
       </c>
       <c r="E22">
         <v>0.61886440015857658</v>
       </c>
       <c r="F22">
-        <v>0.14775274922022719</v>
+        <v>0.23726468311241641</v>
       </c>
       <c r="G22">
         <v>3.7844600067989842E-2</v>
@@ -1035,16 +1038,16 @@
         <v>0.1235219020533762</v>
       </c>
       <c r="C23">
-        <v>1.9489246399779711E-4</v>
+        <v>1.157026293111767E-2</v>
       </c>
       <c r="D23">
-        <v>0.8376859698668524</v>
+        <v>0.52241343597090495</v>
       </c>
       <c r="E23">
         <v>0.50902327282057658</v>
       </c>
       <c r="F23">
-        <v>0.1217369195565955</v>
+        <v>0.19520422428999171</v>
       </c>
       <c r="G23">
         <v>2.7611561027923531E-2</v>
@@ -1061,16 +1064,16 @@
         <v>0.14906104688746361</v>
       </c>
       <c r="C24">
-        <v>2.7893855442276318E-4</v>
+        <v>1.2025905969478629E-2</v>
       </c>
       <c r="D24">
-        <v>0.86539774019417037</v>
+        <v>0.53947388349737591</v>
       </c>
       <c r="E24">
         <v>0.62292584601240863</v>
       </c>
       <c r="F24">
-        <v>0.14735011248451621</v>
+        <v>0.2363718768641325</v>
       </c>
       <c r="G24">
         <v>3.8944090554694631E-2</v>
@@ -1087,16 +1090,16 @@
         <v>0.1468708778877921</v>
       </c>
       <c r="C25">
-        <v>2.7359462849717639E-4</v>
+        <v>1.183065491445858E-2</v>
       </c>
       <c r="D25">
-        <v>0.85136402321950866</v>
+        <v>0.53075312812896158</v>
       </c>
       <c r="E25">
         <v>0.62033234380877944</v>
       </c>
       <c r="F25">
-        <v>0.1472064615648816</v>
+        <v>0.23612915067235171</v>
       </c>
       <c r="G25">
         <v>3.7912923173564067E-2</v>
@@ -1189,16 +1192,16 @@
         <v>9.3845336665548507E-2</v>
       </c>
       <c r="C5">
-        <v>1.1265833287091991E-4</v>
+        <v>1.216759282239608E-2</v>
       </c>
       <c r="D5">
-        <v>0.93501110826463019</v>
+        <v>0.5552577451290347</v>
       </c>
       <c r="E5">
         <v>0.36244354177994792</v>
       </c>
       <c r="F5">
-        <v>7.7379375083253862E-2</v>
+        <v>0.13030088438767179</v>
       </c>
       <c r="G5">
         <v>2.4556886211678879E-2</v>
@@ -1215,16 +1218,16 @@
         <v>8.3788083633156374E-2</v>
       </c>
       <c r="C6">
-        <v>7.393896855881286E-5</v>
+        <v>1.215075613075574E-2</v>
       </c>
       <c r="D6">
-        <v>0.93773885254666323</v>
+        <v>0.55625331089829688</v>
       </c>
       <c r="E6">
         <v>0.31470982636452438</v>
       </c>
       <c r="F6">
-        <v>6.6429285778074096E-2</v>
+        <v>0.1119873284357224</v>
       </c>
       <c r="G6">
         <v>2.0004354945371939E-2</v>
@@ -1241,16 +1244,16 @@
         <v>8.8237536851101916E-2</v>
       </c>
       <c r="C7">
-        <v>8.7700731464151799E-5</v>
+        <v>1.2575803900766999E-2</v>
       </c>
       <c r="D7">
-        <v>0.9695838705126073</v>
+        <v>0.57519806322396583</v>
       </c>
       <c r="E7">
         <v>0.32568256734558132</v>
       </c>
       <c r="F7">
-        <v>6.8836515817538316E-2</v>
+        <v>0.1160344231078945</v>
       </c>
       <c r="G7">
         <v>2.2310706348978009E-2</v>
@@ -1267,16 +1270,16 @@
         <v>9.3780383874903839E-2</v>
       </c>
       <c r="C8">
-        <v>1.102539382324595E-4</v>
+        <v>1.2352116687894351E-2</v>
       </c>
       <c r="D8">
-        <v>0.95158092647211034</v>
+        <v>0.56384292612966225</v>
       </c>
       <c r="E8">
         <v>0.35749249752714829</v>
       </c>
       <c r="F8">
-        <v>7.5963715173195667E-2</v>
+        <v>0.12820170141879211</v>
       </c>
       <c r="G8">
         <v>2.4771139350304741E-2</v>
@@ -1293,16 +1296,16 @@
         <v>9.1210704659218322E-2</v>
       </c>
       <c r="C9">
-        <v>1.031753816206059E-4</v>
+        <v>1.2074023618879879E-2</v>
       </c>
       <c r="D9">
-        <v>0.9278759263245645</v>
+        <v>0.55139203802018388</v>
       </c>
       <c r="E9">
         <v>0.3530381230619532</v>
       </c>
       <c r="F9">
-        <v>7.5134984397365823E-2</v>
+        <v>0.1264362530467579</v>
       </c>
       <c r="G9">
         <v>2.3383014341053429E-2</v>
@@ -1319,16 +1322,16 @@
         <v>8.9211621515346895E-2</v>
       </c>
       <c r="C10">
-        <v>9.1059495468195494E-5</v>
+        <v>1.246154492928277E-2</v>
       </c>
       <c r="D10">
-        <v>0.9625564841899843</v>
+        <v>0.5697553773767815</v>
       </c>
       <c r="E10">
         <v>0.33438511708693208</v>
       </c>
       <c r="F10">
-        <v>7.0351050785556285E-2</v>
+        <v>0.1188525159955352</v>
       </c>
       <c r="G10">
         <v>2.3000814850631691E-2</v>
@@ -1345,16 +1348,16 @@
         <v>9.462103444975134E-2</v>
       </c>
       <c r="C11">
-        <v>1.129613288618414E-4</v>
+        <v>1.226717868648481E-2</v>
       </c>
       <c r="D11">
-        <v>0.94482948511793385</v>
+        <v>0.55980536652958601</v>
       </c>
       <c r="E11">
         <v>0.36625451866594089</v>
       </c>
       <c r="F11">
-        <v>7.7396264817553712E-2</v>
+        <v>0.13062803147271321</v>
       </c>
       <c r="G11">
         <v>2.5484738263012879E-2</v>
@@ -1371,16 +1374,16 @@
         <v>9.3845336665548507E-2</v>
       </c>
       <c r="C12">
-        <v>2.218135906530371E-4</v>
+        <v>1.2590859238878489E-2</v>
       </c>
       <c r="D12">
-        <v>0.79346933275788245</v>
+        <v>0.57267121736366522</v>
       </c>
       <c r="E12">
         <v>0.36244354177994792</v>
       </c>
       <c r="F12">
-        <v>9.1182572868880624E-2</v>
+        <v>0.1263387665727099</v>
       </c>
       <c r="G12">
         <v>4.8953485242434473E-2</v>
@@ -1397,16 +1400,16 @@
         <v>8.3788083633156374E-2</v>
       </c>
       <c r="C13">
-        <v>1.8473437299798101E-4</v>
+        <v>1.245799422355948E-2</v>
       </c>
       <c r="D13">
-        <v>0.78769071193941986</v>
+        <v>0.5682336591448881</v>
       </c>
       <c r="E13">
         <v>0.31470982636452438</v>
       </c>
       <c r="F13">
-        <v>7.9083479437823387E-2</v>
+        <v>0.10962624480001459</v>
       </c>
       <c r="G13">
         <v>4.2220860277898349E-2</v>
@@ -1423,16 +1426,16 @@
         <v>8.8237536851101916E-2</v>
       </c>
       <c r="C14">
-        <v>2.0291336351880489E-4</v>
+        <v>1.2832943235094679E-2</v>
       </c>
       <c r="D14">
-        <v>0.8104312281070567</v>
+        <v>0.5847527778902597</v>
       </c>
       <c r="E14">
         <v>0.32568256734558132</v>
       </c>
       <c r="F14">
-        <v>8.2354644199562482E-2</v>
+        <v>0.1141384495508916</v>
       </c>
       <c r="G14">
         <v>4.5207306740422309E-2</v>
@@ -1449,16 +1452,16 @@
         <v>9.3780383874903839E-2</v>
       </c>
       <c r="C15">
-        <v>2.2225016248487119E-4</v>
+        <v>1.270801123398725E-2</v>
       </c>
       <c r="D15">
-        <v>0.80197944713451186</v>
+        <v>0.57806717868558122</v>
       </c>
       <c r="E15">
         <v>0.35749249752714829</v>
       </c>
       <c r="F15">
-        <v>9.0134008696919815E-2</v>
+        <v>0.12504709682209819</v>
       </c>
       <c r="G15">
         <v>4.8944732607670648E-2</v>
@@ -1475,16 +1478,16 @@
         <v>9.1210704659218322E-2</v>
       </c>
       <c r="C16">
-        <v>2.1204010060296301E-4</v>
+        <v>1.244171252244645E-2</v>
       </c>
       <c r="D16">
-        <v>0.78409265904072378</v>
+        <v>0.5662217436635465</v>
       </c>
       <c r="E16">
         <v>0.3530381230619532</v>
       </c>
       <c r="F16">
-        <v>8.8912888602195997E-2</v>
+        <v>0.12312480759925271</v>
       </c>
       <c r="G16">
         <v>4.6410808393760931E-2</v>
@@ -1501,16 +1504,16 @@
         <v>8.9211621515346895E-2</v>
       </c>
       <c r="C17">
-        <v>2.0620029169048239E-4</v>
+        <v>1.26552496919362E-2</v>
       </c>
       <c r="D17">
-        <v>0.79988386633345054</v>
+        <v>0.57636549210498933</v>
       </c>
       <c r="E17">
         <v>0.33438511708693208</v>
       </c>
       <c r="F17">
-        <v>8.4658364736896335E-2</v>
+        <v>0.1174894420828389</v>
       </c>
       <c r="G17">
         <v>4.5023038459306539E-2</v>
@@ -1527,16 +1530,16 @@
         <v>9.462103444975134E-2</v>
       </c>
       <c r="C18">
-        <v>2.249791531319322E-4</v>
+        <v>1.254578976654575E-2</v>
       </c>
       <c r="D18">
-        <v>0.7912913690539799</v>
+        <v>0.57043099476818282</v>
       </c>
       <c r="E18">
         <v>0.36625451866594089</v>
       </c>
       <c r="F18">
-        <v>9.2413838817736488E-2</v>
+        <v>0.128194775018034</v>
       </c>
       <c r="G18">
         <v>4.8671936175578502E-2</v>
@@ -1553,16 +1556,16 @@
         <v>9.3845336665548507E-2</v>
       </c>
       <c r="C19">
-        <v>9.7192385146427948E-5</v>
+        <v>1.1349605142353491E-2</v>
       </c>
       <c r="D19">
-        <v>0.83935769573376762</v>
+        <v>0.51797623011155747</v>
       </c>
       <c r="E19">
         <v>0.36244354177994792</v>
       </c>
       <c r="F19">
-        <v>8.6197547983602782E-2</v>
+        <v>0.1396793347791952</v>
       </c>
       <c r="G19">
         <v>1.5997905443195039E-2</v>
@@ -1579,16 +1582,16 @@
         <v>8.3788083633156374E-2</v>
       </c>
       <c r="C20">
-        <v>5.7719413373859849E-5</v>
+        <v>1.136049376397631E-2</v>
       </c>
       <c r="D20">
-        <v>0.84414579198039141</v>
+        <v>0.52027978647068007</v>
       </c>
       <c r="E20">
         <v>0.31470982636452438</v>
       </c>
       <c r="F20">
-        <v>7.3794506603987883E-2</v>
+        <v>0.11973042935915799</v>
       </c>
       <c r="G20">
         <v>1.1759865086599141E-2</v>
@@ -1605,16 +1608,16 @@
         <v>8.8237536851101916E-2</v>
       </c>
       <c r="C21">
-        <v>7.159110891798013E-5</v>
+        <v>1.1731242999104351E-2</v>
       </c>
       <c r="D21">
-        <v>0.87063071108042833</v>
+        <v>0.53670967489860655</v>
       </c>
       <c r="E21">
         <v>0.32568256734558132</v>
       </c>
       <c r="F21">
-        <v>7.6660258579834842E-2</v>
+        <v>0.1243554542809014</v>
       </c>
       <c r="G21">
         <v>1.402499764193888E-2</v>
@@ -1631,16 +1634,16 @@
         <v>9.3780383874903839E-2</v>
       </c>
       <c r="C22">
-        <v>9.3977360682035262E-5</v>
+        <v>1.154335702641439E-2</v>
       </c>
       <c r="D22">
-        <v>0.85600406046594457</v>
+        <v>0.52701523256794558</v>
       </c>
       <c r="E22">
         <v>0.35749249752714829</v>
       </c>
       <c r="F22">
-        <v>8.4445420064276508E-2</v>
+        <v>0.13716040447361</v>
       </c>
       <c r="G22">
         <v>1.6247692809060878E-2</v>
@@ -1657,16 +1660,16 @@
         <v>9.1210704659218322E-2</v>
       </c>
       <c r="C23">
-        <v>8.7667373346690571E-5</v>
+        <v>1.1268478845838519E-2</v>
       </c>
       <c r="D23">
-        <v>0.8334810456922801</v>
+        <v>0.5146878870047733</v>
       </c>
       <c r="E23">
         <v>0.3530381230619532</v>
       </c>
       <c r="F23">
-        <v>8.3644305539284619E-2</v>
+        <v>0.13545285406423591</v>
       </c>
       <c r="G23">
         <v>1.483599780456926E-2</v>
@@ -1683,16 +1686,16 @@
         <v>8.9211621515346895E-2</v>
       </c>
       <c r="C24">
-        <v>7.4798578203941971E-5</v>
+        <v>1.163571844982275E-2</v>
       </c>
       <c r="D24">
-        <v>0.86520562922989142</v>
+        <v>0.53213713121395745</v>
       </c>
       <c r="E24">
         <v>0.33438511708693208</v>
       </c>
       <c r="F24">
-        <v>7.8266781693838508E-2</v>
+        <v>0.1272545292014006</v>
       </c>
       <c r="G24">
         <v>1.4474815861008589E-2</v>
@@ -1709,16 +1712,16 @@
         <v>9.462103444975134E-2</v>
       </c>
       <c r="C25">
-        <v>9.6631486465090937E-5</v>
+        <v>1.1471197840972881E-2</v>
       </c>
       <c r="D25">
-        <v>0.85048793086229357</v>
+        <v>0.52357047243802834</v>
       </c>
       <c r="E25">
         <v>0.36625451866594089</v>
       </c>
       <c r="F25">
-        <v>8.5981552922778343E-2</v>
+        <v>0.13966844367121181</v>
       </c>
       <c r="G25">
         <v>1.6685164914523189E-2</v>
@@ -1811,16 +1814,16 @@
         <v>7.7717639036698039E-2</v>
       </c>
       <c r="C5">
-        <v>5.3000629560509479E-5</v>
+        <v>1.206083945345687E-2</v>
       </c>
       <c r="D5">
-        <v>0.93310517602804277</v>
+        <v>0.55306752980242402</v>
       </c>
       <c r="E5">
         <v>0.2837794072342078</v>
       </c>
       <c r="F5">
-        <v>6.0253526685910871E-2</v>
+        <v>0.10165644264933089</v>
       </c>
       <c r="G5">
         <v>1.6669445524167392E-2</v>
@@ -1837,16 +1840,16 @@
         <v>7.0889224137377305E-2</v>
       </c>
       <c r="C6">
-        <v>2.617396298637499E-5</v>
+        <v>1.199427020197049E-2</v>
       </c>
       <c r="D6">
-        <v>0.935830377119648</v>
+        <v>0.55116727988368353</v>
       </c>
       <c r="E6">
         <v>0.25071984964513783</v>
       </c>
       <c r="F6">
-        <v>5.2781426990300938E-2</v>
+        <v>8.9617915518625385E-2</v>
       </c>
       <c r="G6">
         <v>1.335985184232236E-2</v>
@@ -1863,16 +1866,16 @@
         <v>5.4846136391674787E-2</v>
       </c>
       <c r="C7">
-        <v>-3.7529501086241313E-5</v>
+        <v>1.2383776780162691E-2</v>
       </c>
       <c r="D7">
-        <v>0.96945229924041298</v>
+        <v>0.57206077439003489</v>
       </c>
       <c r="E7">
         <v>0.16428869606920329</v>
       </c>
       <c r="F7">
-        <v>3.4402285708822929E-2</v>
+        <v>5.8300405258698611E-2</v>
       </c>
       <c r="G7">
         <v>5.4618474341022894E-3</v>
@@ -1889,16 +1892,16 @@
         <v>7.5791014749006624E-2</v>
       </c>
       <c r="C8">
-        <v>4.3528816550176603E-5</v>
+        <v>1.222998328914068E-2</v>
       </c>
       <c r="D8">
-        <v>0.95101843724463975</v>
+        <v>0.56124597225123296</v>
       </c>
       <c r="E8">
         <v>0.27026499034981738</v>
       </c>
       <c r="F8">
-        <v>5.7092745219731907E-2</v>
+        <v>9.6742348313140242E-2</v>
       </c>
       <c r="G8">
         <v>1.59742257098675E-2</v>
@@ -1915,16 +1918,16 @@
         <v>7.2022544778493014E-2</v>
       </c>
       <c r="C9">
-        <v>3.1812197555414369E-5</v>
+        <v>1.195433478963252E-2</v>
       </c>
       <c r="D9">
-        <v>0.92652723593245956</v>
+        <v>0.54913733860175096</v>
       </c>
       <c r="E9">
         <v>0.25801590655059709</v>
       </c>
       <c r="F9">
-        <v>5.4534590465126383E-2</v>
+        <v>9.2013017171659328E-2</v>
       </c>
       <c r="G9">
         <v>1.376859799189338E-2</v>
@@ -1941,16 +1944,16 @@
         <v>5.3656134290635649E-2</v>
       </c>
       <c r="C10">
-        <v>-4.2508842122341038E-5</v>
+        <v>1.228755303852991E-2</v>
       </c>
       <c r="D10">
-        <v>0.96381020164046849</v>
+        <v>0.56784078294942475</v>
       </c>
       <c r="E10">
         <v>0.16031670781666829</v>
       </c>
       <c r="F10">
-        <v>3.3368989894238588E-2</v>
+        <v>5.6638011647305947E-2</v>
       </c>
       <c r="G10">
         <v>4.6792073921171811E-3</v>
@@ -1967,16 +1970,16 @@
         <v>6.9776371353649225E-2</v>
       </c>
       <c r="C11">
-        <v>2.09873257857738E-5</v>
+        <v>1.21062438847353E-2</v>
       </c>
       <c r="D11">
-        <v>0.94344077297582762</v>
+        <v>0.55658147620387444</v>
       </c>
       <c r="E11">
         <v>0.24366765825792641</v>
       </c>
       <c r="F11">
-        <v>5.1176090036078467E-2</v>
+        <v>8.6746706467523513E-2</v>
       </c>
       <c r="G11">
         <v>1.290543394865163E-2</v>
@@ -1993,16 +1996,16 @@
         <v>7.7717639036698039E-2</v>
       </c>
       <c r="C12">
-        <v>1.623574163192734E-4</v>
+        <v>1.2451393257714371E-2</v>
       </c>
       <c r="D12">
-        <v>0.78925536623353443</v>
+        <v>0.56895984503869934</v>
       </c>
       <c r="E12">
         <v>0.2837794072342078</v>
       </c>
       <c r="F12">
-        <v>7.1235344135666387E-2</v>
+        <v>9.8816951872487735E-2</v>
       </c>
       <c r="G12">
         <v>3.8482141716427637E-2</v>
@@ -2019,16 +2022,16 @@
         <v>7.0889224137377305E-2</v>
       </c>
       <c r="C13">
-        <v>1.3728178000847209E-4</v>
+        <v>1.2278042061817989E-2</v>
       </c>
       <c r="D13">
-        <v>0.78279377451564924</v>
+        <v>0.56207156715530948</v>
       </c>
       <c r="E13">
         <v>0.25071984964513783</v>
       </c>
       <c r="F13">
-        <v>6.3100224265080732E-2</v>
+        <v>8.7879312193705067E-2</v>
       </c>
       <c r="G13">
         <v>3.3173986410036271E-2</v>
@@ -2045,16 +2048,16 @@
         <v>5.4846136391674787E-2</v>
       </c>
       <c r="C14">
-        <v>7.8950687340446489E-5</v>
+        <v>1.2543532727980301E-2</v>
       </c>
       <c r="D14">
-        <v>0.80246364906400425</v>
+        <v>0.57707253541727188</v>
       </c>
       <c r="E14">
         <v>0.16428869606920329</v>
       </c>
       <c r="F14">
-        <v>4.1561228372705893E-2</v>
+        <v>5.779407775043071E-2</v>
       </c>
       <c r="G14">
         <v>2.299765986915624E-2</v>
@@ -2071,16 +2074,16 @@
         <v>7.5791014749006624E-2</v>
       </c>
       <c r="C15">
-        <v>1.5632664713452609E-4</v>
+        <v>1.2521141297240799E-2</v>
       </c>
       <c r="D15">
-        <v>0.79619137258624684</v>
+        <v>0.57245245481935991</v>
       </c>
       <c r="E15">
         <v>0.27026499034981738</v>
       </c>
       <c r="F15">
-        <v>6.8194978250651947E-2</v>
+        <v>9.4848494193302504E-2</v>
       </c>
       <c r="G15">
         <v>3.6763872222577189E-2</v>
@@ -2097,16 +2100,16 @@
         <v>7.2022544778493014E-2</v>
       </c>
       <c r="C16">
-        <v>1.4119109424154511E-4</v>
+        <v>1.2269469043619601E-2</v>
       </c>
       <c r="D16">
-        <v>0.77883543319731585</v>
+        <v>0.56151777780555634</v>
       </c>
       <c r="E16">
         <v>0.25801590655059709</v>
       </c>
       <c r="F16">
-        <v>6.4876071648323597E-2</v>
+        <v>8.9984298562776913E-2</v>
       </c>
       <c r="G16">
         <v>3.3820080719317441E-2</v>
@@ -2123,16 +2126,16 @@
         <v>5.3656134290635649E-2</v>
       </c>
       <c r="C17">
-        <v>7.4373791768396832E-5</v>
+        <v>1.2353087616456961E-2</v>
       </c>
       <c r="D17">
-        <v>0.79117791551848504</v>
+        <v>0.56846219925843322</v>
       </c>
       <c r="E17">
         <v>0.16031670781666829</v>
       </c>
       <c r="F17">
-        <v>4.064998813500556E-2</v>
+        <v>5.657609761996453E-2</v>
       </c>
       <c r="G17">
         <v>2.1522723703587342E-2</v>
@@ -2149,16 +2152,16 @@
         <v>6.9776371353649225E-2</v>
       </c>
       <c r="C18">
-        <v>1.3389643484305351E-4</v>
+        <v>1.230355566315804E-2</v>
       </c>
       <c r="D18">
-        <v>0.78366235817843477</v>
+        <v>0.56341708029403814</v>
       </c>
       <c r="E18">
         <v>0.24366765825792641</v>
       </c>
       <c r="F18">
-        <v>6.1610219551370887E-2</v>
+        <v>8.5694260309469208E-2</v>
       </c>
       <c r="G18">
         <v>3.1893891576797222E-2</v>
@@ -2175,16 +2178,16 @@
         <v>7.7717639036698039E-2</v>
       </c>
       <c r="C19">
-        <v>3.7334950302600532E-5</v>
+        <v>1.125535320952656E-2</v>
       </c>
       <c r="D19">
-        <v>0.83841034873483256</v>
+        <v>0.51636988532066275</v>
       </c>
       <c r="E19">
         <v>0.2837794072342078</v>
       </c>
       <c r="F19">
-        <v>6.7058902254019143E-2</v>
+        <v>0.1088810157657687</v>
       </c>
       <c r="G19">
         <v>8.8973811707361069E-3</v>
@@ -2201,16 +2204,16 @@
         <v>7.0889224137377305E-2</v>
       </c>
       <c r="C20">
-        <v>9.8265968271756769E-6</v>
+        <v>1.121693580377366E-2</v>
       </c>
       <c r="D20">
-        <v>0.84295882142967071</v>
+        <v>0.5157912328271862</v>
       </c>
       <c r="E20">
         <v>0.25071984964513783</v>
       </c>
       <c r="F20">
-        <v>5.859653101615659E-2</v>
+        <v>9.5764448058767063E-2</v>
       </c>
       <c r="G20">
         <v>5.8329311386017321E-3</v>
@@ -2227,16 +2230,16 @@
         <v>5.4846136391674787E-2</v>
       </c>
       <c r="C21">
-        <v>-5.4122190318522153E-5</v>
+        <v>1.1563050092939949E-2</v>
       </c>
       <c r="D21">
-        <v>0.87211485700122904</v>
+        <v>0.53468786991930084</v>
       </c>
       <c r="E21">
         <v>0.16428869606920329</v>
       </c>
       <c r="F21">
-        <v>3.8241952549946057E-2</v>
+        <v>6.2375409759300567E-2</v>
       </c>
       <c r="G21">
         <v>-1.041886037192576E-3</v>
@@ -2253,16 +2256,16 @@
         <v>7.5791014749006624E-2</v>
       </c>
       <c r="C22">
-        <v>2.6903828036280269E-5</v>
+        <v>1.143921026253663E-2</v>
       </c>
       <c r="D22">
-        <v>0.85668027888169607</v>
+        <v>0.52525957197497675</v>
       </c>
       <c r="E22">
         <v>0.27026499034981738</v>
       </c>
       <c r="F22">
-        <v>6.3379833381659881E-2</v>
+        <v>0.1033703262802462</v>
       </c>
       <c r="G22">
         <v>8.3236585771941114E-3</v>
@@ -2279,16 +2282,16 @@
         <v>7.2022544778493014E-2</v>
       </c>
       <c r="C23">
-        <v>1.609999576357278E-5</v>
+        <v>1.116107191013796E-2</v>
       </c>
       <c r="D23">
-        <v>0.83301823175196155</v>
+        <v>0.51300657413240669</v>
       </c>
       <c r="E23">
         <v>0.25801590655059709</v>
       </c>
       <c r="F23">
-        <v>6.0656275505632989E-2</v>
+        <v>9.8493442217216148E-2</v>
       </c>
       <c r="G23">
         <v>6.2033736557442843E-3</v>
@@ -2305,16 +2308,16 @@
         <v>5.3656134290635649E-2</v>
       </c>
       <c r="C24">
-        <v>-5.9284833386530762E-5</v>
+        <v>1.1484255330059491E-2</v>
       </c>
       <c r="D24">
-        <v>0.86796337219025121</v>
+        <v>0.53127927554780974</v>
       </c>
       <c r="E24">
         <v>0.16031670781666829</v>
       </c>
       <c r="F24">
-        <v>3.705383649697986E-2</v>
+        <v>6.0535718893500581E-2</v>
       </c>
       <c r="G24">
         <v>-1.872387069657014E-3</v>
@@ -2331,16 +2334,16 @@
         <v>6.9776371353649225E-2</v>
       </c>
       <c r="C25">
-        <v>4.3123944765900866E-6</v>
+        <v>1.132956173517387E-2</v>
       </c>
       <c r="D25">
-        <v>0.85045660755264907</v>
+        <v>0.52124826556076786</v>
       </c>
       <c r="E25">
         <v>0.24366765825792641</v>
       </c>
       <c r="F25">
-        <v>5.6771397285580463E-2</v>
+        <v>9.2626898028286456E-2</v>
       </c>
       <c r="G25">
         <v>5.4355894349854463E-3</v>
